--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
   <si>
     <t>##var</t>
   </si>
@@ -444,22 +444,16 @@
     <t>Cue逻辑基类</t>
   </si>
   <si>
-    <t>HeadlessAutoBattleNoopCue</t>
-  </si>
-  <si>
-    <t>Cue: HeadlessAutoBattleNoopCue</t>
+    <t>AutoChessNoopCue</t>
+  </si>
+  <si>
+    <t>Cue: AutoChessNoopCue</t>
   </si>
   <si>
     <t>Param</t>
   </si>
   <si>
     <t>参数</t>
-  </si>
-  <si>
-    <t>HeadlessAutoChessNoopCue</t>
-  </si>
-  <si>
-    <t>Cue: HeadlessAutoChessNoopCue</t>
   </si>
   <si>
     <t>CueLog</t>
@@ -1035,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="1:88"/>
+  <dimension ref="1:87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="20.6640625" customWidth="1" style="5"/>
@@ -1923,7 +1917,7 @@
         <v>145</v>
       </c>
       <c r="L65" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N65" s="3" t="s">
         <v>146</v>
@@ -1943,7 +1937,7 @@
         <v>145</v>
       </c>
       <c r="L66" s="5" t="s">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>146</v>
@@ -1963,7 +1957,7 @@
         <v>145</v>
       </c>
       <c r="L67" s="5" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="N67" s="3" t="s">
         <v>146</v>
@@ -1983,7 +1977,7 @@
         <v>145</v>
       </c>
       <c r="L68" s="5" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="N68" s="3" t="s">
         <v>146</v>
@@ -2003,57 +1997,57 @@
         <v>145</v>
       </c>
       <c r="L69" s="5" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="N69" s="3" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="5" t="s">
+      <c r="A70" s="9"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+      <c r="M70" s="8"/>
+      <c r="N70" s="9"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G70" s="5" t="s">
+      <c r="C71" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G71" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="J70" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="L70" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="N70" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="9"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="8"/>
-      <c r="N71" s="9"/>
     </row>
     <row r="72">
       <c r="B72" s="5" t="s">
         <v>159</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>160</v>
+      </c>
+      <c r="J72" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="L72" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="73">
@@ -2061,7 +2055,7 @@
         <v>161</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>162</v>
@@ -2070,57 +2064,57 @@
         <v>145</v>
       </c>
       <c r="L73" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N73" s="3" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="5" t="s">
+      <c r="A74" s="9"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
+      <c r="N74" s="9"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G74" s="5" t="s">
+      <c r="C75" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G75" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="J74" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="L74" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="N74" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="9"/>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
-      <c r="I75" s="8"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
-      <c r="L75" s="8"/>
-      <c r="M75" s="8"/>
-      <c r="N75" s="9"/>
     </row>
     <row r="76">
       <c r="B76" s="5" t="s">
         <v>165</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>166</v>
+      </c>
+      <c r="J76" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="L76" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="77">
@@ -2128,7 +2122,7 @@
         <v>167</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>168</v>
@@ -2137,7 +2131,7 @@
         <v>145</v>
       </c>
       <c r="L77" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N77" s="3" t="s">
         <v>146</v>
@@ -2148,7 +2142,7 @@
         <v>169</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>170</v>
@@ -2157,7 +2151,7 @@
         <v>145</v>
       </c>
       <c r="L78" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N78" s="3" t="s">
         <v>146</v>
@@ -2168,7 +2162,7 @@
         <v>171</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>172</v>
@@ -2188,7 +2182,7 @@
         <v>173</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>174</v>
@@ -2197,7 +2191,7 @@
         <v>145</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="N80" s="3" t="s">
         <v>146</v>
@@ -2208,7 +2202,7 @@
         <v>175</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>176</v>
@@ -2217,7 +2211,7 @@
         <v>145</v>
       </c>
       <c r="L81" s="5" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>146</v>
@@ -2228,7 +2222,7 @@
         <v>177</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>178</v>
@@ -2237,57 +2231,57 @@
         <v>145</v>
       </c>
       <c r="L82" s="5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="N82" s="3" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="5" t="s">
+      <c r="A83" s="9"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="8"/>
+      <c r="M83" s="8"/>
+      <c r="N83" s="9"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G84" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C83" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G83" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="J83" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="L83" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="9"/>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="8"/>
-      <c r="I84" s="8"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="8"/>
-      <c r="L84" s="8"/>
-      <c r="M84" s="8"/>
-      <c r="N84" s="9"/>
     </row>
     <row r="85">
       <c r="B85" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C85" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>181</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="L85" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N85" s="3" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="86">
@@ -2304,7 +2298,7 @@
         <v>145</v>
       </c>
       <c r="L86" s="5" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="N86" s="3" t="s">
         <v>146</v>
@@ -2327,26 +2321,6 @@
         <v>133</v>
       </c>
       <c r="N87" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="J88" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="L88" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="N88" s="3" t="s">
         <v>146</v>
       </c>
     </row>
